--- a/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
@@ -624,7 +624,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2891
+</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">259
@@ -633,50 +638,45 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -715,7 +715,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
@@ -727,12 +727,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>132</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -765,7 +765,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4645
+</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2651</t>
@@ -773,7 +778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -813,7 +818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -826,36 +831,38 @@
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">77
+990
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">223
+</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1839
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -885,13 +892,13 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -909,13 +916,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -933,14 +940,10 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>01400</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">12
@@ -949,13 +952,13 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -966,38 +969,37 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">042
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8261
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1015,7 +1017,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1025,19 +1027,19 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">9310
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1055,7 +1057,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552
+          <t xml:space="preserve">3552
 </t>
         </is>
       </c>
@@ -1079,54 +1081,57 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
-</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
+          <t xml:space="preserve">1771
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1138,7 +1143,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1150,13 +1155,13 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1168,25 +1173,25 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1204,7 +1209,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3279
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1222,62 +1227,60 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2131
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13189
+          <t xml:space="preserve">127219
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1295,13 +1298,13 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1319,7 +1322,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
@@ -1331,7 +1334,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -1350,7 +1353,8 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1366,43 +1370,51 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">1342
+</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
-</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n"/>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -1415,13 +1427,13 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">8929
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">056
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
@@ -1445,7 +1457,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -1457,7 +1469,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1472,31 +1484,29 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1506,17 +1516,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">150
@@ -1529,63 +1539,67 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16379
+</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">430
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">541
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1901
 </t>
         </is>
       </c>
@@ -1597,7 +1611,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1615,113 +1629,127 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
+          <t xml:space="preserve">77871
+</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2531
+228548177
+</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11975
-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>017</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">986
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1817
-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1736,67 +1764,63 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>041</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1789
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">277275
+163
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1808,19 +1832,19 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1838,25 +1862,24 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">8850
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1874,19 +1897,20 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1897,63 +1921,58 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">001
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -1962,16 +1981,16 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">668
@@ -1980,7 +1999,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
@@ -1998,17 +2017,22 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -2024,7 +2048,7 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2036,117 +2060,123 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3561
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9908
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9979
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2065
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">23
 </t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1144</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -2165,13 +2195,13 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2183,13 +2213,14 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2200,16 +2231,11 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3252
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
           <t>44</t>
@@ -2217,20 +2243,25 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184883
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">9226
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -2248,13 +2279,13 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2265,12 +2296,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>83</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2298,16 +2329,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2319,25 +2350,25 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">4236
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4819
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2349,81 +2380,82 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>121</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">9416
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>553</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40948</t>
+          <t xml:space="preserve">1004
+</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2441,7 +2473,8 @@
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t xml:space="preserve">2579
+</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2452,8 +2485,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2464,13 +2496,13 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">4891
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -2480,41 +2512,30 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>222</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">034
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4381
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">237
@@ -2523,30 +2544,29 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>431</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
-</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2558,7 +2578,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11909
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -2570,7 +2590,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2595,30 +2615,31 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1397
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">98
 </t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2630,7 +2651,8 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -2642,76 +2664,72 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9986
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>124</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7420
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">767
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>6340880</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2726,57 +2744,70 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 85 2
+</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>214251</t>
+          <t xml:space="preserve">233
+</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+      <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -2787,13 +2818,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -2805,7 +2835,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2816,13 +2846,13 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2853,22 +2883,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">93
@@ -2877,7 +2902,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -2889,24 +2914,24 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2918,58 +2943,53 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>131</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1912
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -2994,12 +3014,13 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3011,7 +3032,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3023,102 +3044,102 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1266
+</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">809
-</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -3137,7 +3158,8 @@
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3148,64 +3170,65 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2121
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">165
 </t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11888
-</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1060
+</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">246
@@ -3220,49 +3243,49 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2891
+</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1892
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">889
-</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
@@ -3292,25 +3315,25 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3334,30 +3357,36 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">066
+</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3370,14 +3399,13 @@
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3280
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3394,7 +3422,8 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">261
+</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3405,7 +3434,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>763</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3420,30 +3449,29 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1256
-</t>
-        </is>
-      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3454,15 +3482,14 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7017
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3473,17 +3500,16 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
-      </c>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">231
@@ -3492,55 +3518,54 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">3281
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1731
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>9300407</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3557,55 +3582,41 @@
         </is>
       </c>
       <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122 1
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">372
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3616,69 +3627,48 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111561
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr"/>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n"/>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="inlineStr"/>
-      <c r="Y25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4158
+41419
+</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="n"/>
+      <c r="Z25" s="2" t="n"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3691,68 +3681,64 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
+      <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">115178685
+1149791
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>153</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -3764,60 +3750,62 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">064
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1153
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -3833,128 +3821,133 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">7155
+</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">379
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">153
 </t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>043</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000
-</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -3970,16 +3963,21 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -3989,15 +3987,10 @@
 </t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -4008,93 +4001,93 @@
 </t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
+      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21610
+</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">9360
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4113,129 +4106,135 @@
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>51</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">2150
+</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">990
 </t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>4343</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1310
-</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -4253,14 +4252,19 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11168
-</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -4272,19 +4276,19 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4293,92 +4297,99 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42138
+          <t xml:space="preserve">667
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>42501</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4395,46 +4406,41 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n"/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+89191911
+</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">943
+</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">769
@@ -4443,7 +4449,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -4455,51 +4461,54 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
+          <t>99921</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">2272
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">959
+</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4132
+</t>
+        </is>
+      </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1635
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -4511,12 +4520,13 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">81911955
+111
 </t>
         </is>
       </c>
@@ -4534,7 +4544,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0884
+          <t xml:space="preserve">3646
 </t>
         </is>
       </c>
@@ -4546,7 +4556,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144 1
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
@@ -4558,7 +4568,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4570,20 +4580,20 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">7116
 </t>
         </is>
       </c>
@@ -4595,73 +4605,79 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809
+          <t xml:space="preserve">2007
 </t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">4781
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">19 1 6
+</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70 6
+</t>
+        </is>
+      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 84
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 13
+          <t xml:space="preserve">18 1
 </t>
         </is>
       </c>
@@ -4679,34 +4695,34 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
+          <t xml:space="preserve">4402
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
@@ -4715,92 +4731,92 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>393</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4816,13 +4832,13 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1197
-</t>
-        </is>
-      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">137
@@ -4831,14 +4847,13 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4846,41 +4861,41 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -4889,51 +4904,56 @@
           <t>212</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4952,7 +4972,8 @@
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4963,30 +4984,30 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -4998,20 +5019,23 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">452
+</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
@@ -5023,48 +5047,43 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">9868
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5076,7 +5095,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2186
+          <t xml:space="preserve">384
 </t>
         </is>
       </c>
@@ -5095,130 +5114,136 @@
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1227
+</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1079
+</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">759
+</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">665
+</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1664
-</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2920
-</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5237,7 +5262,7 @@
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5249,7 +5274,8 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">422112
+214101
 </t>
         </is>
       </c>
@@ -5259,28 +5285,36 @@
 </t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">455266
+72
+45
+61194929
+</t>
+        </is>
+      </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
@@ -5292,13 +5326,13 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9878
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -5310,13 +5344,13 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -5327,15 +5361,22 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t xml:space="preserve">2191
+</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">816
@@ -5344,17 +5385,18 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">4225
+</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5370,119 +5412,131 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>44841</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n"/>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6813
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">676
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21372
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
+          <t xml:space="preserve">4960
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180
-</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr"/>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8792
+</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3809
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">664
-</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5500,12 +5554,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>143</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -5523,108 +5577,94 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">777
+141
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
+          <t xml:space="preserve">1381
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1810
-</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t xml:space="preserve">661
+</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
       <c r="X39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">165
 </t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">670
-</t>
-        </is>
-      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5642,7 +5682,8 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
+          <t xml:space="preserve">227
+6443
 </t>
         </is>
       </c>
@@ -5653,13 +5694,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5671,78 +5712,79 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">789
+</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -5754,13 +5796,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5771,7 +5812,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5787,12 +5828,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4088
-</t>
-        </is>
-      </c>
+      <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -5801,7 +5837,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11597
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -5819,7 +5855,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>343</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5830,71 +5866,71 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1013
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">700
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1726
+</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">470
-</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
           <t>217</t>
@@ -5908,19 +5944,19 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1853
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5938,13 +5974,13 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6094
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -5961,38 +5997,40 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">472
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">56
+</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -6010,20 +6048,15 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
       <c r="S42" s="2" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
@@ -6035,7 +6068,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6047,7 +6080,7 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -6058,7 +6091,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
@@ -6076,144 +6109,124 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">60944
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">7064
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
-</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111416 1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1207
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7119
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -6231,77 +6244,109 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
-</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">622
+2722208602828
+</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">2124
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550020
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101101101
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="2" t="n"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10110
-</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1501151000115
-</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119898
+          <t xml:space="preserve">24222
+7
 </t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr"/>
-      <c r="Y44" s="2" t="inlineStr"/>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6314,10 +6359,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31195
+</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">672727
+</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -6327,7 +6378,8 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">84
+24222
 </t>
         </is>
       </c>
@@ -6339,22 +6391,17 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6363,24 +6410,20 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6022
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6219
+          <t xml:space="preserve">61972
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4980
+          <t xml:space="preserve">6242
 </t>
         </is>
       </c>
@@ -6391,55 +6434,55 @@
 </t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">892
-</t>
-        </is>
-      </c>
+      <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">8272
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29298
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
+          <t xml:space="preserve">12089
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3288
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="n"/>
+          <t xml:space="preserve">378
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6454,24 +6497,25 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t xml:space="preserve">107
+</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6489,45 +6533,43 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">3821
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1044
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6538,34 +6580,39 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="n"/>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929180
+</t>
+        </is>
+      </c>
       <c r="W46" s="2" t="n"/>
       <c r="X46" s="2" t="n"/>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6580,6 +6627,48 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">551
+</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
@@ -632,125 +632,127 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">71138
 </t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2108
+</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12668
+</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -767,24 +769,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
+          <t xml:space="preserve">15643
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -795,18 +797,18 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -818,7 +820,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -828,41 +830,39 @@
 </t>
         </is>
       </c>
-      <c r="N5" s="2" t="n"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-990
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -874,13 +874,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -890,18 +889,8 @@
 </t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
+      <c r="Y5" s="2" t="n"/>
+      <c r="Z5" s="2" t="n"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2</t>
@@ -916,20 +905,19 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
+          <t xml:space="preserve">3380
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -940,25 +928,30 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>01400</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111416
+</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -969,43 +962,42 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">09942
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1161
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">6718
 </t>
         </is>
       </c>
@@ -1017,29 +1009,24 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="n"/>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9310
+          <t xml:space="preserve">1930
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">11039
 </t>
         </is>
       </c>
@@ -1057,7 +1044,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3552
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
@@ -1069,129 +1056,112 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">2801
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1771
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
+          <t xml:space="preserve">2985
+</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770
+</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">94
 </t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
-</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="n"/>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1209,132 +1179,132 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3779
+</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2121
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149712
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">72
 </t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127219
-</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">19178
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">1850
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
@@ -1350,71 +1320,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1825281
+</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1260
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t xml:space="preserve">550
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1427,49 +1396,51 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8929
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">1956
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t xml:space="preserve">9988
+</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">8712
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4290
+          <t xml:space="preserve">194290
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1484,45 +1455,40 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3650
+</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1535,71 +1501,53 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16379
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">430
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541
-</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="n"/>
+      <c r="W10" s="2" t="n"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1611,7 +1559,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
@@ -1629,127 +1577,127 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77871
+          <t xml:space="preserve">3296
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2531
-228548177
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t xml:space="preserve">1107
+</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">2016
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t xml:space="preserve">1223
+</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>18114</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">12895
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">720
+</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">74
+</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t xml:space="preserve">1186
+</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">1181
+</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1764,64 +1712,81 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t xml:space="preserve">5212
+</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n"/>
+          <t xml:space="preserve">2317
+</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1139
+</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277275
-163
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">2999
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1832,19 +1797,19 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">2172
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1469
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
@@ -1856,30 +1821,31 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850
+          <t xml:space="preserve">2840
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -1897,44 +1863,41 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">94556
+</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">21138
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1945,34 +1908,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t xml:space="preserve">17176
+</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -1981,25 +1949,24 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>493</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2011,25 +1978,25 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">078
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2045,79 +2012,81 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203199
+</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3561
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9908
+          <t xml:space="preserve">18202
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9979
+          <t xml:space="preserve">9290
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2139,44 +2108,34 @@
 </t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065
-</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="n"/>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
@@ -2192,7 +2151,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4845
+</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">267
@@ -2201,110 +2165,94 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11007
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3252
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1016
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184883
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9226
-</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+      <c r="X15" s="2" t="n"/>
       <c r="Y15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">848
@@ -2313,7 +2261,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -2331,44 +2279,43 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">23269
+</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1272
 </t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">2957
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4236
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1954819
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2380,82 +2327,89 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1669
+</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">194910
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t xml:space="preserve">929
+</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t xml:space="preserve">9290
+</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2470,72 +2424,76 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4145</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579
+          <t xml:space="preserve">2592
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">653
-</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">11191
+</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">18241
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4891
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">1139
+</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4381
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">237
@@ -2544,53 +2502,53 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">5626
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t xml:space="preserve">1112
+</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2014
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">8980
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">2974
 </t>
         </is>
       </c>
@@ -2606,22 +2564,27 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3357
+</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -2633,103 +2596,89 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1940
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">1229
+</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">27190
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2102
+</t>
+        </is>
+      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">767
+          <t xml:space="preserve">5167
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>6340880</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2746,68 +2695,74 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 85 2
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">111626
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1968
+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>143</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -2823,36 +2778,32 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1561
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">1199
+</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">8948
 </t>
         </is>
       </c>
@@ -2874,76 +2825,70 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4949
+</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">112494
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2954,48 +2899,44 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">175
+</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1167
+</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="n"/>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>434</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="n"/>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3011,46 +2952,56 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3793
+</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n"/>
+          <t xml:space="preserve">11796
+</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">2888
+</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -3062,24 +3013,20 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3091,7 +3038,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3101,48 +3048,33 @@
 </t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+      <c r="T21" s="2" t="n"/>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">11694
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="n"/>
+      <c r="Z21" s="2" t="n"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3155,140 +3087,126 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5089
+</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>458</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">21132
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n"/>
+          <t xml:space="preserve">1295
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1016
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1892
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="n"/>
       <c r="AA22" t="inlineStr">
         <is>
           <t>15</t>
@@ -3303,138 +3221,137 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">20894
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">11285
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">11614
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">294890
+</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">066
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">11136
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr"/>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1918
+</t>
+        </is>
+      </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">23280
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t xml:space="preserve">12198
+</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">1863
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
+          <t xml:space="preserve">94290
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3451,124 +3368,110 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
+          <t xml:space="preserve">4379 18
+</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10256
+</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6215659
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1139
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">978
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">2399
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="n"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3281
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
-</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1731
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11894
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="n"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>9300407</t>
+          <t xml:space="preserve">188812
+</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="n"/>
       <c r="AA24" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3581,94 +3484,132 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2336
+</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122 1
-</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n"/>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28726
+</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1136
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">372
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="n"/>
+          <t xml:space="preserve">1020
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="n"/>
-      <c r="S25" s="2" t="n"/>
+          <t xml:space="preserve">5189
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="U25" s="2" t="n"/>
-      <c r="V25" s="2" t="n"/>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4158
-41419
-</t>
-        </is>
-      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="n"/>
-      <c r="Z25" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3681,128 +3622,136 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2583
+</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">11189
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115178685
-1149791
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>016</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1828
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">9318
+</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">0153
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -3818,136 +3767,125 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5358
+</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">12245
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155
+          <t xml:space="preserve">7133
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">11189
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">379
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20916
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">11835
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="n"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="n"/>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3965,129 +3903,126 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n"/>
+          <t xml:space="preserve">11817
+</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>445</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21610
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9360
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>422</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4103,138 +4038,129 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3091
+</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">131
+</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2150
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">9910
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="n"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8561
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1858
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">119910
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4252,54 +4178,55 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">15699
+</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1168
 </t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">15449
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">16294
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">1769
 </t>
         </is>
       </c>
@@ -4309,87 +4236,70 @@
 </t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>4449244</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">2121
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">667
+          <t xml:space="preserve">94138
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1829
+</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr"/>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">9220
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4406,127 +4316,129 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">3140
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-89191911
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n"/>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">908
+</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">769
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">084
+</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>99921</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">024
+</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2272
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4132
+          <t xml:space="preserve">81154
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">1063
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">1 85
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>42221</t>
+          <t xml:space="preserve">950
+</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81911955
-111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4544,143 +4456,105 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3646
+          <t xml:space="preserve">3642
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">2579
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">128213
+</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7116
+          <t xml:space="preserve">7196
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2007
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4781
-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19 1 6
-</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">911
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="n"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70 6
-</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="n"/>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18 1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">960
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="n"/>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -4695,128 +4569,126 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4402
+          <t xml:space="preserve">4112
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">1132
+</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t xml:space="preserve">11817
+</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">11000
+</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110972
+</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">201912
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
-</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="n"/>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">2916
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">19800
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -4834,126 +4706,121 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
+          <t>11444</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1197
+</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11452
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2990
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1426
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1292
-</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">778
-</t>
-        </is>
-      </c>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -4969,136 +4836,135 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4778
+</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">1121
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
+          <t xml:space="preserve">1212818
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9868
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="n"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>484</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">384
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2840
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="n"/>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5111,139 +4977,133 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6132
+</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">759
+          <t xml:space="preserve">11150
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">665
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11616
+</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="n"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>412</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5259,145 +5119,142 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>197824</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">11184
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">422112
-214101
+          <t xml:space="preserve">10922
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">455266
-72
-45
-61194929
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">16815
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">94920
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
-</t>
+          <t>3821914</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2332
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">1816
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">880
+</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4225
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5414,129 +5271,122 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>44841</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4956
+</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">1741
+</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1913
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21372
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2190
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4960
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">034
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8792
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">11720
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">1664
+</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181014
+</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="n"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">01846
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -5554,114 +5404,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">6243
+</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
-141
-</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2193
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121202
+</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
+          <t xml:space="preserve">2012
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1505
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr"/>
-      <c r="W39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="n"/>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1988
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1628
+</t>
+        </is>
+      </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">32
@@ -5682,25 +5539,25 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-6443
+          <t xml:space="preserve">6377
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -5710,64 +5567,64 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">11100
+</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2354
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -5778,41 +5635,42 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">0488
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5828,138 +5686,114 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7943
+</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1013
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11208
+</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">179
 </t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">700
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1726
-</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">488
-</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t xml:space="preserve">2 1 4
+</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="n"/>
+      <c r="Z41" s="2" t="n"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -5980,66 +5814,61 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24709
+</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="n"/>
+          <t xml:space="preserve">11605
+</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">359
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">04
@@ -6048,15 +5877,25 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">9490
 </t>
         </is>
       </c>
@@ -6068,30 +5907,31 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">158
+</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6109,77 +5949,74 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60944
+          <t xml:space="preserve">6044
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7064
-</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="n"/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1810
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7119
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
+          <t>4340</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6191,19 +6028,19 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6212,21 +6049,16 @@
           <t>160</t>
         </is>
       </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
+      <c r="X43" s="2" t="n"/>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
+          <t xml:space="preserve">7298
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6242,111 +6074,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">622
-2722208602828
-</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2124
-</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
       <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr"/>
-      <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24222
-7
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr"/>
-      <c r="X44" s="2" t="inlineStr"/>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="n"/>
+      <c r="U44" s="2" t="n"/>
+      <c r="V44" s="2" t="n"/>
+      <c r="W44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
+      <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6367,19 +6118,18 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672727
-</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t xml:space="preserve">036
+</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-24222
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6391,95 +6141,113 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">11819
+</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6022
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">3564
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">559
+</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61972
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6242
-</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr"/>
+          <t>4960</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">11263
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8272
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">12822
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12089
+          <t xml:space="preserve">11089
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">10609
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">378
+          <t xml:space="preserve">23028 1
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6497,31 +6265,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2239
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">15034
 </t>
         </is>
       </c>
@@ -6533,89 +6300,81 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3821
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1595
 </t>
         </is>
       </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">11113
+</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2353
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="n"/>
+      <c r="T46" s="2" t="n"/>
       <c r="U46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18654
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929180
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="n"/>
-      <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+      <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6627,48 +6386,6 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">551
-</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
@@ -632,13 +632,13 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -648,16 +648,21 @@
 </t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -669,7 +674,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -681,13 +686,13 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -699,19 +704,20 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">8202
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12668
+          <t xml:space="preserve">8197
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1893
+</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -726,15 +732,21 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="2" t="n"/>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
@@ -744,17 +756,8 @@
 </t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2930
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -769,19 +772,20 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15643
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1140
+</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -792,7 +796,8 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -803,24 +808,25 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -838,19 +844,25 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
+          <t xml:space="preserve">958
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -874,12 +886,13 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
@@ -889,8 +902,18 @@
 </t>
         </is>
       </c>
-      <c r="Y5" s="2" t="n"/>
-      <c r="Z5" s="2" t="n"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2</t>
@@ -911,29 +934,31 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">1049
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">101
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416
+          <t xml:space="preserve">11106
 </t>
         </is>
       </c>
@@ -945,30 +970,31 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09942
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">1215621
 </t>
         </is>
       </c>
@@ -978,7 +1004,12 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -987,17 +1018,19 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6718
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
@@ -1009,27 +1042,29 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="n"/>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11039
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="n"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1044,7 +1079,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
+          <t xml:space="preserve">2552
 </t>
         </is>
       </c>
@@ -1056,7 +1091,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -1068,23 +1103,25 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2801
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -1096,12 +1133,14 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1112,11 +1151,16 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2985
-</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -1125,10 +1169,16 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">770
@@ -1143,19 +1193,25 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="n"/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1179,7 +1235,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
+          <t xml:space="preserve">3778
 </t>
         </is>
       </c>
@@ -1197,47 +1253,55 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">2141
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149712
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
@@ -1249,26 +1313,31 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -1280,13 +1349,13 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19178
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -1298,13 +1367,13 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1322,17 +1391,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825281
+          <t xml:space="preserve">18252
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n"/>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">715
+</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">990
@@ -1341,13 +1415,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">050
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
@@ -1359,38 +1433,49 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">12819
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">749
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">4238
+</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1402,20 +1487,25 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">9856
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9988
-</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">09101
+</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">955
 </t>
         </is>
       </c>
@@ -1427,19 +1517,19 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">9498
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194290
+          <t xml:space="preserve">942908
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -1457,7 +1547,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
+          <t xml:space="preserve">36501
 </t>
         </is>
       </c>
@@ -1469,17 +1559,28 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">412
+</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">13
@@ -1488,26 +1589,31 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1580
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1517,10 +1623,15 @@
 </t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83 8
+</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1542,9 +1653,23 @@
 </t>
         </is>
       </c>
-      <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n"/>
-      <c r="W10" s="2" t="n"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -1553,13 +1678,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1587,8 +1712,18 @@
 </t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1853
+</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1139
+</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">101
@@ -1597,67 +1732,73 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">097
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n"/>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">527
+</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">1623
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12895
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1669,13 +1810,13 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -1687,17 +1828,22 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1712,104 +1858,109 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5212
+          <t xml:space="preserve">5811
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2317
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2539
+</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2198
+</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0800
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">090
+</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1139
 </t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2999
-</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2172
-</t>
-        </is>
-      </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">141046
 </t>
         </is>
       </c>
@@ -1821,13 +1972,13 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -1839,13 +1990,13 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1863,7 +2014,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94556
+          <t xml:space="preserve">5556
 </t>
         </is>
       </c>
@@ -1875,29 +2026,32 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t xml:space="preserve">2216
+</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21138
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1914,30 +2068,31 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17176
+          <t xml:space="preserve">8196
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1949,7 +2104,8 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1960,16 +2116,11 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -1978,13 +2129,13 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">078
+          <t xml:space="preserve">1978
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -1996,7 +2147,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2014,7 +2165,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203199
+          <t xml:space="preserve">0318
 </t>
         </is>
       </c>
@@ -2026,67 +2177,73 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t xml:space="preserve">2045
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">96
+</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">1125
+</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18202
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9290
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2108,25 +2265,36 @@
 </t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711
+</t>
+        </is>
+      </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="n"/>
+          <t xml:space="preserve">1184
+</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">840
@@ -2135,7 +2303,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2165,47 +2333,64 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11007
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
+          <t xml:space="preserve">2120821
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">970
@@ -2214,13 +2399,14 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">2257
+</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -2237,25 +2423,37 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="n"/>
+          <t xml:space="preserve">96480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="n"/>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">8248
 </t>
         </is>
       </c>
@@ -2279,7 +2477,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23269
+          <t xml:space="preserve">230691
 </t>
         </is>
       </c>
@@ -2291,31 +2489,37 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">643
+</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2957
+          <t xml:space="preserve">957
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1954819
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n"/>
+          <t xml:space="preserve">589
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1397
+</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -2327,36 +2531,37 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194910
+          <t xml:space="preserve">4818
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">11157
 </t>
         </is>
       </c>
@@ -2380,35 +2585,37 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">558
+</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t xml:space="preserve">11004
+</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9290
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -2426,35 +2633,38 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t xml:space="preserve">48141
+</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">1130
+</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11191
+          <t xml:space="preserve">1971
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18241
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2465,10 +2675,16 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n"/>
+          <t xml:space="preserve">2164
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1139
@@ -2477,20 +2693,25 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2502,7 +2723,8 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2513,42 +2735,43 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5626
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2974
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -2566,13 +2789,13 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357
+          <t xml:space="preserve">9557
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2009
 </t>
         </is>
       </c>
@@ -2584,54 +2807,79 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">8191
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n"/>
+          <t xml:space="preserve">11822
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">9809
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -2643,42 +2891,44 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102
+          <t xml:space="preserve">2106
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">680
+</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2695,30 +2945,31 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111626
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">11993
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2728,29 +2979,40 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">1642
+</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="n"/>
+          <t xml:space="preserve">2108
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -2762,7 +3024,8 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -2773,37 +3036,43 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">1794
+</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">361
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">11995
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">1985
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -2827,59 +3096,71 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4949
-</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+          <t xml:space="preserve">14949
+</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">022
+</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112494
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">11958
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n"/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n"/>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">280
@@ -2888,13 +3169,14 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t xml:space="preserve">1035
+</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -2909,34 +3191,45 @@
 </t>
         </is>
       </c>
-      <c r="T20" s="2" t="n"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880
+</t>
+        </is>
+      </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t xml:space="preserve">2588
+</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -2954,48 +3247,49 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
+          <t xml:space="preserve">3713
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">2036
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">8916080
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">1198
+</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11796
+          <t xml:space="preserve">1956
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2888
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -3013,20 +3307,25 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n"/>
+          <t xml:space="preserve">1163
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1887
+</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">18080
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3044,26 +3343,31 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">947
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11694
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -3073,7 +3377,12 @@
 </t>
         </is>
       </c>
-      <c r="Y21" s="2" t="n"/>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
       <c r="Z21" s="2" t="n"/>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3095,97 +3404,110 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t xml:space="preserve">2258
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21132
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">517
+</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">127
 </t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1195
-</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1046
+</t>
+        </is>
+      </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">18 7
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3197,7 +3519,8 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3206,7 +3529,12 @@
 </t>
         </is>
       </c>
-      <c r="Z22" s="2" t="n"/>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>15</t>
@@ -3233,18 +3561,19 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">975
+</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11614
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3256,13 +3585,13 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -3274,83 +3603,91 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">2071
+</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294890
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1
+</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11136
+          <t xml:space="preserve">115136
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t xml:space="preserve">915
+</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23280
+          <t xml:space="preserve">3280
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12198
+          <t xml:space="preserve">1498
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">9389
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
+          <t xml:space="preserve">4298
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">11963
 </t>
         </is>
       </c>
@@ -3368,30 +3705,40 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4379 18
+          <t xml:space="preserve">49729
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10256
+          <t xml:space="preserve">0256
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n"/>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6215659
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n"/>
+          <t xml:space="preserve">1234
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1085
+</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">22
@@ -3400,14 +3747,20 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n"/>
+          <t xml:space="preserve">597
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 4
+</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3416,7 +3769,12 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="2" t="n"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">978
@@ -3425,24 +3783,31 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399
+          <t xml:space="preserve">2919
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="n"/>
+          <t xml:space="preserve">1853
+</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -3454,14 +3819,19 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11894
-</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="n"/>
+          <t xml:space="preserve">1894
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1731
+</t>
+        </is>
+      </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188812
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -3471,7 +3841,12 @@
 </t>
         </is>
       </c>
-      <c r="Z24" s="2" t="n"/>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3486,91 +3861,97 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
+          <t xml:space="preserve">2536
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">11539
+</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28726
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">121356
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">1962
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3582,31 +3963,43 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="n"/>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1719
+</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3624,7 +4017,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2583
+          <t xml:space="preserve">2683
 </t>
         </is>
       </c>
@@ -3636,19 +4029,19 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3666,44 +4059,55 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="n"/>
+          <t xml:space="preserve">11158
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">888080
+</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -3715,13 +4119,13 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9318
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3733,25 +4137,25 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0153
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -3769,81 +4173,98 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5358
+          <t xml:space="preserve">93517
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">013125
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20916
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">0116
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1117
+</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="K27" s="2" t="n"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11835
+          <t xml:space="preserve">1735
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="n"/>
+          <t xml:space="preserve">2258
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1018
+</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3866,7 +4287,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -3876,10 +4297,15 @@
 </t>
         </is>
       </c>
-      <c r="X27" s="2" t="n"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3903,7 +4329,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
@@ -3921,7 +4347,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3933,50 +4359,68 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8075
+</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">03
+</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">980
 </t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t xml:space="preserve">1170
+</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3987,13 +4431,13 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4005,7 +4449,8 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">1170
+</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
@@ -4052,66 +4497,78 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n"/>
+          <t xml:space="preserve">20185
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11122
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">1150
+</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9910
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4121,10 +4578,15 @@
 </t>
         </is>
       </c>
-      <c r="S29" s="2" t="n"/>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8561
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
@@ -4136,31 +4598,31 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1858
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119910
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1794
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4196,19 +4658,19 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15449
+          <t xml:space="preserve">6499
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16294
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -4220,38 +4682,49 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
+          <t xml:space="preserve">749
+</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">745
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4449244</t>
+          <t xml:space="preserve">4910
+</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121
+          <t xml:space="preserve">4121
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">9989
 </t>
         </is>
       </c>
@@ -4263,43 +4736,50 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94138
+          <t xml:space="preserve">41351
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">857
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
-</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">8294
+</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220
+          <t xml:space="preserve">65480
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4322,7 +4802,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -4340,47 +4820,56 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1125
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n"/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1150
 </t>
         </is>
       </c>
-      <c r="M31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">14544
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4391,45 +4880,40 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1078
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81154
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">180101
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1063
-</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr"/>
       <c r="Y31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">950
@@ -4438,7 +4922,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -4462,66 +4946,73 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t xml:space="preserve">1319
+</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128213
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>793</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7196
+          <t xml:space="preserve">2116
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">751
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -4537,24 +5028,54 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="2" t="n"/>
-      <c r="T32" s="2" t="n"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr"/>
-      <c r="W32" s="2" t="inlineStr"/>
-      <c r="X32" s="2" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1266
+</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11817
+</t>
+        </is>
+      </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="n"/>
+          <t xml:space="preserve">1960
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -4581,7 +5102,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -4593,48 +5114,55 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">110080
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1115
+</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1049
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110972
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">9628
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4646,49 +5174,61 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201912
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="n"/>
-      <c r="T33" s="2" t="n"/>
+          <t xml:space="preserve">1864
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">718
+</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2916
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">1165
+</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19800
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4706,18 +5246,19 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t xml:space="preserve">2114
+</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">11972
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">11597
 </t>
         </is>
       </c>
@@ -4729,98 +5270,121 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11452
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">003
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">985
+</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1969
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="n"/>
-      <c r="T34" s="2" t="n"/>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1169
-</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">1866
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4844,7 +5408,8 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4855,7 +5420,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">21818
 </t>
         </is>
       </c>
@@ -4873,12 +5438,13 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4896,13 +5462,13 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212818
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
@@ -4920,22 +5486,28 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">118
@@ -4944,27 +5516,34 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="n"/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -4985,42 +5564,43 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">17138
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t xml:space="preserve">10995
+</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">11059
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5032,49 +5612,61 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11150
+          <t xml:space="preserve">0120
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11616
-</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5086,24 +5678,25 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5121,7 +5714,8 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>197824</t>
+          <t xml:space="preserve">20782
+</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -5132,30 +5726,31 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10922
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">8194
 </t>
         </is>
       </c>
@@ -5167,76 +5762,79 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
+          <t xml:space="preserve">50717
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16815
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94920
+          <t xml:space="preserve">4920
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t xml:space="preserve">1010
+</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3821914</t>
+          <t xml:space="preserve">3809
+</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2332
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>209</t>
+          <t xml:space="preserve">900
+</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
@@ -5248,13 +5846,14 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">4299
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5275,81 +5874,98 @@
 </t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">10251
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1913
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t xml:space="preserve">1135
+</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">11170
+</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11720
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -5361,32 +5977,37 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181014
-</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="n"/>
+          <t xml:space="preserve">1801
+</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01846
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -5404,7 +6025,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
+          <t xml:space="preserve">6641
 </t>
         </is>
       </c>
@@ -5416,13 +6037,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5434,32 +6055,38 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n"/>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2193
-</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121202
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5471,57 +6098,67 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">1698
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1505
+          <t xml:space="preserve">15210
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr"/>
-      <c r="W39" s="2" t="n"/>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1275
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0625
+</t>
+        </is>
+      </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1988
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5545,13 +6182,13 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5563,7 +6200,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -5582,13 +6219,13 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11100
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
@@ -5600,7 +6237,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -5612,30 +6249,31 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2354
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0488
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
@@ -5647,30 +6285,31 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">173
+</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -5688,7 +6327,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7943
+          <t xml:space="preserve">6943
 </t>
         </is>
       </c>
@@ -5698,101 +6337,132 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="2" t="n"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1726
+</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 37
+</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">01107
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">1053
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11208
-</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">12935
+</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">581
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">470
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 1 4
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="2" t="n"/>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
       <c r="Z41" s="2" t="n"/>
       <c r="AA41" t="inlineStr">
         <is>
@@ -5808,7 +6478,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
@@ -5820,37 +6490,37 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24709
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11605
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">538
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">359
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5860,15 +6530,25 @@
 </t>
         </is>
       </c>
-      <c r="L42" s="2" t="n"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">04
@@ -5877,7 +6557,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -5889,19 +6569,19 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1474
 </t>
         </is>
       </c>
@@ -5913,25 +6593,25 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -5949,65 +6629,83 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
+          <t xml:space="preserve">6094
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">16 279
+</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2" t="n"/>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110219
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1521
+</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">248
@@ -6028,37 +6726,38 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t xml:space="preserve">1680
+</t>
         </is>
       </c>
       <c r="X43" s="2" t="n"/>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7298
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2119
 </t>
         </is>
       </c>
@@ -6074,7 +6773,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
@@ -6118,18 +6822,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t xml:space="preserve">1319
+</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">036
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -6147,7 +6852,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11819
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
@@ -6159,13 +6864,13 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">0800
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3564
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
@@ -6177,77 +6882,79 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t xml:space="preserve">4900
+</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12822
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11089
+          <t xml:space="preserve">1089
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10609
+          <t xml:space="preserve">6580
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028 1
+          <t xml:space="preserve">3828
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">2815
 </t>
         </is>
       </c>
@@ -6271,74 +6978,85 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t xml:space="preserve">11015
+</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15034
+          <t xml:space="preserve">12004
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="n"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111110
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11113
+          <t xml:space="preserve">112198
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">11119
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="n"/>
+          <t xml:space="preserve">1351
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9001
+</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">0241
 </t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2353
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6348,8 +7066,18 @@
 </t>
         </is>
       </c>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="n"/>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598
+</t>
+        </is>
+      </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">18654
@@ -6358,24 +7086,29 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">215416
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="n"/>
       <c r="X46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="Y46" s="2" t="n"/>
-      <c r="Z46" s="2" t="n"/>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -686,7 +686,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -698,25 +698,25 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8202
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8197
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1893
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -728,7 +728,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -746,7 +746,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -772,7 +772,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">146495
 </t>
         </is>
       </c>
@@ -784,13 +784,13 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -820,7 +820,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -844,7 +844,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -886,13 +886,13 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -910,8 +910,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -934,19 +933,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1049
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -958,7 +957,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -976,25 +975,25 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215621
+          <t xml:space="preserve">12561
 </t>
         </is>
       </c>
@@ -1004,12 +1003,7 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -1054,7 +1048,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -1079,7 +1073,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552
+          <t xml:space="preserve">3537
 </t>
         </is>
       </c>
@@ -1097,7 +1091,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1133,7 +1127,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -1151,7 +1145,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1175,19 +1169,19 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1235,7 +1229,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3778
+          <t xml:space="preserve">3779
 </t>
         </is>
       </c>
@@ -1247,13 +1241,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -1277,7 +1271,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1289,31 +1283,31 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1349,13 +1343,13 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1403,7 +1397,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">713
 </t>
         </is>
       </c>
@@ -1415,7 +1409,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -1431,15 +1425,10 @@
 </t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12819
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -1451,31 +1440,31 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4238
+          <t xml:space="preserve">4220
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1033
 </t>
         </is>
       </c>
@@ -1487,13 +1476,13 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9856
+          <t xml:space="preserve">92856
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09101
+          <t xml:space="preserve">8911
 </t>
         </is>
       </c>
@@ -1517,19 +1506,19 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9498
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942908
+          <t xml:space="preserve">94298
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -1559,7 +1548,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -1571,13 +1560,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -1589,31 +1578,31 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1625,7 +1614,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83 8
+          <t xml:space="preserve">6 2
 </t>
         </is>
       </c>
@@ -1649,24 +1638,25 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">191
 </t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1708,19 +1698,19 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">1333
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -1750,25 +1740,25 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">2 316
 </t>
         </is>
       </c>
@@ -1780,13 +1770,13 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623
+          <t xml:space="preserve">1023
 </t>
         </is>
       </c>
@@ -1798,7 +1788,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2899
 </t>
         </is>
       </c>
@@ -1810,31 +1800,31 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">11886
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">2184
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -1858,7 +1848,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5811
+          <t xml:space="preserve">5011
 </t>
         </is>
       </c>
@@ -1870,7 +1860,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -1882,13 +1872,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0800
+          <t xml:space="preserve">01100
 </t>
         </is>
       </c>
@@ -1898,12 +1888,7 @@
 </t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -1912,7 +1897,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
@@ -1924,19 +1909,19 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1948,19 +1933,19 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141046
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1996,7 +1981,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2014,7 +1999,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5556
+          <t xml:space="preserve">1556
 </t>
         </is>
       </c>
@@ -2026,19 +2011,19 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -2068,19 +2053,19 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8196
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -2092,7 +2077,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2110,7 +2095,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
@@ -2120,7 +2105,12 @@
 </t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -2129,7 +2119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2147,7 +2137,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2165,13 +2155,13 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0318
+          <t xml:space="preserve">0329
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2189,7 +2179,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2045
+          <t xml:space="preserve">0145
 </t>
         </is>
       </c>
@@ -2207,13 +2197,13 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2231,7 +2221,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
@@ -2267,13 +2257,13 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
+          <t xml:space="preserve">1711
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2285,13 +2275,13 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -2321,7 +2311,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
+          <t xml:space="preserve">4545
 </t>
         </is>
       </c>
@@ -2333,61 +2323,61 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1149
 </t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2120821
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1199
-</t>
-        </is>
-      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2405,7 +2395,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -2423,13 +2413,13 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96480
+          <t xml:space="preserve">2480
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2441,19 +2431,19 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -2477,7 +2467,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230691
+          <t xml:space="preserve">23069
 </t>
         </is>
       </c>
@@ -2489,7 +2479,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">643
+          <t xml:space="preserve">6553
 </t>
         </is>
       </c>
@@ -2507,37 +2497,37 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">589
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1349
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">669
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2549,19 +2539,19 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4818
+          <t xml:space="preserve">4930
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11157
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2591,7 +2581,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11004
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
@@ -2603,13 +2593,13 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
+          <t xml:space="preserve">94210
 </t>
         </is>
       </c>
@@ -2633,13 +2623,13 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48141
+          <t xml:space="preserve">08141
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -2651,13 +2641,13 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1971
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -2675,19 +2665,18 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -2699,13 +2688,13 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2729,7 +2718,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -2771,7 +2760,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2795,7 +2784,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2807,37 +2796,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2849,31 +2833,31 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11822
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9809
+          <t xml:space="preserve">9828
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">12168
 </t>
         </is>
       </c>
@@ -2891,31 +2875,31 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2106
+          <t xml:space="preserve">2102
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16 7
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -2927,7 +2911,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -2945,7 +2929,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
@@ -2957,13 +2941,13 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1630
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11993
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -2987,7 +2971,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2999,20 +2983,25 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -3024,7 +3013,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -3036,7 +3025,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3048,25 +3037,25 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11995
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
@@ -3096,25 +3085,25 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14949
+          <t xml:space="preserve">14979
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11958
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -3132,31 +3121,31 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3169,13 +3158,13 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1035
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -3187,13 +3176,13 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3205,13 +3194,13 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1912
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2588
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
@@ -3223,7 +3212,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -3253,13 +3242,13 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8916080
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
@@ -3271,19 +3260,19 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3307,7 +3296,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">2163
 </t>
         </is>
       </c>
@@ -3319,7 +3308,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18080
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -3343,7 +3332,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3355,7 +3344,7 @@
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -3367,19 +3356,19 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3404,26 +3393,25 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3438,7 +3426,12 @@
 </t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">517
@@ -3447,19 +3440,19 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">11209
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3471,19 +3464,19 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1046
+          <t xml:space="preserve">12246
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 7
+          <t xml:space="preserve">18 54
 </t>
         </is>
       </c>
@@ -3495,13 +3488,13 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3519,7 +3512,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -3555,7 +3548,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11285
+          <t xml:space="preserve">11284
 </t>
         </is>
       </c>
@@ -3573,7 +3566,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
@@ -3603,19 +3596,19 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2071
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
@@ -3625,39 +3618,28 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115136
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9185
+</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3280
-</t>
+          <t>32606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
+          <t xml:space="preserve">0498
 </t>
         </is>
       </c>
@@ -3669,13 +3651,13 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9389
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -3687,7 +3669,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11963
+          <t xml:space="preserve">1983
 </t>
         </is>
       </c>
@@ -3705,13 +3687,13 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49729
+          <t xml:space="preserve">49129
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0256
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
@@ -3735,7 +3717,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1085
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -3747,19 +3729,14 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">597
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">371
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3771,7 +3748,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3783,19 +3760,19 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">0944
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2919
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3807,7 +3784,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -3825,7 +3802,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1731
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3843,7 +3820,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3861,19 +3838,19 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2536
+          <t xml:space="preserve">2236
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">23 1
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11539
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -3885,19 +3862,18 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121356
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -3909,13 +3885,13 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3927,49 +3903,49 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -3981,7 +3957,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3993,13 +3969,13 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">9208
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4035,40 +4011,35 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">177
 </t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -4077,7 +4048,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -4089,19 +4060,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888080
+          <t xml:space="preserve">9088
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4119,7 +4090,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -4137,19 +4108,19 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
@@ -4173,7 +4144,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93517
+          <t xml:space="preserve">4358
 </t>
         </is>
       </c>
@@ -4197,19 +4168,19 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">013125
+          <t xml:space="preserve">01312
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4227,19 +4198,19 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1735
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
+          <t xml:space="preserve">1088
 </t>
         </is>
       </c>
@@ -4251,13 +4222,13 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -4273,12 +4244,7 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
+      <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -4287,7 +4253,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4305,7 +4271,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -4329,7 +4295,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
@@ -4347,25 +4313,25 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8075
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -4389,7 +4355,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -4431,13 +4397,13 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4491,28 +4457,23 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20185
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">122
@@ -4539,7 +4500,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>37</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -4568,7 +4529,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -4604,13 +4565,13 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4622,7 +4583,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4664,7 +4625,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6499
+          <t xml:space="preserve">6459
 </t>
         </is>
       </c>
@@ -4682,7 +4643,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -4694,37 +4655,32 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4910
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4918
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9989
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
@@ -4736,13 +4692,13 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41351
+          <t xml:space="preserve">4131
 </t>
         </is>
       </c>
@@ -4754,31 +4710,31 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8294
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65480
+          <t xml:space="preserve">942280
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -4808,7 +4764,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -4826,25 +4782,25 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4863,15 +4819,11 @@
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14544
-</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16441
+</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -4880,7 +4832,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1078
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -4892,24 +4844,25 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">92116
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180101
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4922,7 +4875,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4946,13 +4899,13 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -4970,7 +4923,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
@@ -4982,34 +4935,39 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>291</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">751
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">82
@@ -5024,13 +4982,13 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -5042,13 +5000,13 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -5060,19 +5018,19 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5102,7 +5060,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
@@ -5114,13 +5072,13 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110080
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">2115
 </t>
         </is>
       </c>
@@ -5144,19 +5102,19 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1049
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9628
+          <t xml:space="preserve">1601
 </t>
         </is>
       </c>
@@ -5174,61 +5132,61 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">0165
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5252,13 +5210,13 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11972
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11597
+          <t xml:space="preserve">15719
 </t>
         </is>
       </c>
@@ -5270,7 +5228,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -5288,37 +5246,32 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">003
+          <t xml:space="preserve">023
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5330,7 +5283,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1969
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -5348,7 +5301,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -5360,7 +5313,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -5372,13 +5325,13 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -5402,13 +5355,13 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -5420,13 +5373,13 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21818
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -5444,7 +5397,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -5466,12 +5419,7 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
-      </c>
+      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -5480,25 +5428,25 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
@@ -5516,7 +5464,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -5528,7 +5476,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5564,19 +5512,19 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10995
+          <t xml:space="preserve">0195
 </t>
         </is>
       </c>
@@ -5588,13 +5536,13 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11059
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -5612,7 +5560,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0120
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -5624,25 +5572,25 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8708
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5660,19 +5608,19 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5684,13 +5632,13 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5750,7 +5698,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8194
+          <t xml:space="preserve">1814
 </t>
         </is>
       </c>
@@ -5762,7 +5710,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50717
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
@@ -5774,13 +5722,13 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5792,7 +5740,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5810,19 +5758,19 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
+          <t xml:space="preserve">38019
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -5846,13 +5794,13 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4299
+          <t xml:space="preserve">4222
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -5870,14 +5818,13 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4956
+          <t xml:space="preserve">4156
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>837</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5888,25 +5835,25 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10251
+          <t xml:space="preserve">10351
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">1665
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">11702
 </t>
         </is>
       </c>
@@ -5918,7 +5865,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5941,13 +5888,13 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">984
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">02 4
 </t>
         </is>
       </c>
@@ -5959,13 +5906,13 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
@@ -5977,13 +5924,13 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1 6 1
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -6001,13 +5948,13 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6025,7 +5972,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6641
+          <t xml:space="preserve">6244
 </t>
         </is>
       </c>
@@ -6037,7 +5984,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
@@ -6074,7 +6021,7 @@
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6086,14 +6033,13 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -6104,7 +6050,7 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -6116,25 +6062,25 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15210
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -6146,13 +6092,13 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -6225,13 +6171,13 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6249,13 +6195,13 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -6267,7 +6213,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -6285,7 +6231,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6309,7 +6255,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6327,25 +6273,25 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6943
+          <t xml:space="preserve">6993
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
@@ -6355,12 +6301,7 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 37
-</t>
-        </is>
-      </c>
+      <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">47
@@ -6369,7 +6310,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6381,19 +6322,19 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1053
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6411,55 +6352,55 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12935
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1722
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">581
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">26417
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -6478,7 +6419,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
@@ -6490,7 +6431,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6502,25 +6443,25 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6532,20 +6473,20 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6557,7 +6498,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
@@ -6581,7 +6522,7 @@
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -6599,19 +6540,19 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6629,7 +6570,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6094
+          <t xml:space="preserve">50494
 </t>
         </is>
       </c>
@@ -6648,7 +6589,7 @@
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 279
+          <t xml:space="preserve">1 279
 </t>
         </is>
       </c>
@@ -6684,25 +6625,25 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110219
+          <t xml:space="preserve">11227
 </t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9720
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6726,13 +6667,13 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6744,20 +6685,20 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="n"/>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
@@ -6828,13 +6769,13 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6858,19 +6799,19 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
@@ -6888,13 +6829,13 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -6912,20 +6853,19 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">21725
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -6936,25 +6876,25 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">837
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3828
+          <t xml:space="preserve">3028
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2815
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -6984,25 +6924,25 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11015
+          <t xml:space="preserve">11014
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12004
+          <t xml:space="preserve">810154
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -7020,31 +6960,31 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111110
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112198
+          <t xml:space="preserve">112138
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11119
+          <t xml:space="preserve">11019
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1351
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9001
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -7062,7 +7002,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -7080,13 +7020,13 @@
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18654
+          <t xml:space="preserve">13654
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215416
+          <t xml:space="preserve">218416
 </t>
         </is>
       </c>
@@ -7099,13 +7039,13 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
@@ -626,127 +626,127 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
+          <t xml:space="preserve">3012
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">9280
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">4625
 </t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -756,8 +756,18 @@
 </t>
         </is>
       </c>
-      <c r="Y4" s="2" t="n"/>
-      <c r="Z4" s="2" t="n"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738
+</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -772,145 +782,141 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146495
+          <t xml:space="preserve">3824
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1594
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">181494
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">4695
+</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -927,138 +933,148 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
+          <t xml:space="preserve">3091
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1011
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1154
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">116
 </t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12561
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="n"/>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">029
+</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1073,145 +1089,145 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3537
+          <t xml:space="preserve">2758
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">050
+</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0177
+</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">48
 </t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -1229,145 +1245,144 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
+          <t xml:space="preserve">3912
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2673
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">227194
 </t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1385,140 +1400,143 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18252
-</t>
+          <t>439274</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">713
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">739
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">979
+</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">552
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">551
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">6848
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
+          <t xml:space="preserve">1015
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92856
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8911
+          <t xml:space="preserve">38015
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8712
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94298
+          <t xml:space="preserve">94145
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1536,145 +1554,140 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36501
+          <t xml:space="preserve">3499
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">24181
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">2130
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 2
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">7 24
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1692,145 +1705,140 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
+          <t xml:space="preserve">5093
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1333
+          <t xml:space="preserve">10479
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">2110
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">097
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
+      <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 316
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2899
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">5120
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11886
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -1848,140 +1856,145 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5011
+          <t xml:space="preserve">5061
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">2059
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01100
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">11917
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">8221
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">370
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1999,145 +2012,145 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">3579
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1809
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">17915
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -2155,145 +2168,140 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0329
+          <t xml:space="preserve">2270
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0145
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">2158
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1469
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1711
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1595
 </t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">087
 </t>
         </is>
       </c>
@@ -2311,97 +2319,97 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4545
+          <t xml:space="preserve">6310
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1726
 </t>
         </is>
       </c>
@@ -2413,43 +2421,43 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2467,145 +2475,144 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23069
+          <t xml:space="preserve">22271
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6553
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">712
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">395
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1349
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">669
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4930
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">11110
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">3109
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">8017
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94210
+          <t xml:space="preserve">3690
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
@@ -2623,144 +2630,139 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08141
+          <t xml:space="preserve">4459
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">1994
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">98718
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2778,140 +2780,145 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9557
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116666
+</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21104
+</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">96
 </t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9828
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12168
-</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 7
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
@@ -2929,145 +2936,145 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
+          <t xml:space="preserve">5319
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">21112
 </t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">13 0
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">0094
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3085,140 +3092,145 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14979
+          <t xml:space="preserve">5422
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">805
+</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1335
+</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22110
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">405
+</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">222
 </t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1912
-</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">12997
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3236,143 +3248,148 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">3824
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">0159
 </t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3387,66 +3404,67 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
+          <t xml:space="preserve">94890
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11209
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3458,73 +3476,73 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12246
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 54
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1497
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">538
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">505
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -3542,134 +3560,144 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20894
+          <t xml:space="preserve">123203
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11284
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">2611
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2930
+</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9185
-</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr"/>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">781
+</t>
+        </is>
+      </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t xml:space="preserve">2357
+</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0498
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">1067
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
+          <t xml:space="preserve">3415
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -3687,140 +3715,139 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49129
+          <t xml:space="preserve">24641
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1571
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
+          <t xml:space="preserve">7161
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0944
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">11771
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3838,144 +3865,145 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">14889
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 1
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">136
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">2415
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1376
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">01132
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">82169
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -3993,140 +4021,145 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2683
+          <t xml:space="preserve">3499
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">51094
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1158
 </t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9088
-</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
+          <t xml:space="preserve">1550
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -4144,140 +4177,144 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4358
+          <t xml:space="preserve">3402
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1171
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01312
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">094
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116182
+</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1185
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1135
-</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1088
-</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr"/>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4295,145 +4332,145 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
+          <t xml:space="preserve">5133
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">11565
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19354
+</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">680
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28170
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1910
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="Z28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4451,139 +4488,145 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">3233
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1960
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1270
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11817
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">478
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">13
 </t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4601,140 +4644,140 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15699
+          <t xml:space="preserve">22848
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1312
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6459
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">690
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">567
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">4890
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">867
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4131
+          <t xml:space="preserve">3148
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">995
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8249
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942280
+          <t xml:space="preserve">3650
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
@@ -4752,130 +4795,140 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140
+          <t xml:space="preserve">4320
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">26 2
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">1584
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">391
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">978
+</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7193
+</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1169
+</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111 1
+</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1199
 </t>
         </is>
       </c>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16441
-</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92116
-</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1080
-</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -4893,144 +4946,140 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3642
+          <t xml:space="preserve">52808
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">2201
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="n"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">2179
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1700
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5048,148 +5097,143 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
+          <t xml:space="preserve">3491
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">11114
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0165
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">830
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="n"/>
       <c r="AA33" t="inlineStr">
         <is>
           <t>22</t>
@@ -5204,143 +5248,142 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114
+          <t xml:space="preserve">3299
 </t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15719
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">1497
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">023
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1159
+</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">9910
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">330
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="n"/>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -5355,61 +5398,61 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">5067
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
@@ -5419,76 +5462,81 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">8168
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">6835
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5506,49 +5554,49 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6132
+          <t xml:space="preserve">5355
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">11054
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0195
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -5560,94 +5608,88 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">050
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="n"/>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5662,73 +5704,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20782
-</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11184
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">6726
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">1417
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
@@ -5740,67 +5781,66 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38019
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">8371
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4222
+          <t xml:space="preserve">3595
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">394
 </t>
         </is>
       </c>
@@ -5818,72 +5858,69 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4156
+          <t xml:space="preserve">4481
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10351
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11702
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5894,67 +5931,67 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02 4
+          <t xml:space="preserve">3 8
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11276
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 6 1
-</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -5972,142 +6009,137 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6244
+          <t xml:space="preserve">5799
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">2110
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">051
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="n"/>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1025
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t xml:space="preserve">980
+</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0625
+          <t xml:space="preserve">8157
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="n"/>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -6122,25 +6154,25 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -6150,19 +6182,19 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="2" t="n"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83
+</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6171,91 +6203,81 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">489
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="n"/>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6273,44 +6295,39 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6993
+          <t xml:space="preserve">4512
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6322,20 +6339,19 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">8 6
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -6352,59 +6368,64 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1722
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">4235
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26417
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="n"/>
+          <t xml:space="preserve">580
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0198
+</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6419,49 +6440,49 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
+          <t xml:space="preserve">5294
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">113517
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6473,89 +6494,74 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1876
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">2127
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">435
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">610
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="n"/>
+      <c r="X42" s="2" t="n"/>
+      <c r="Y42" s="2" t="n"/>
+      <c r="Z42" s="2" t="n"/>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6570,138 +6576,33 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50494
-</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 279
-</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1130
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11227
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9720
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="n"/>
+      <c r="U43" s="2" t="n"/>
+      <c r="V43" s="2" t="n"/>
+      <c r="W43" s="2" t="n"/>
       <c r="X43" s="2" t="n"/>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2109
-</t>
-        </is>
-      </c>
+      <c r="Y43" s="2" t="n"/>
+      <c r="Z43" s="2" t="n"/>
       <c r="AA43" t="inlineStr">
         <is>
           <t>30</t>
@@ -6757,144 +6658,145 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
+          <t xml:space="preserve">19112
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">10917
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">3880
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21725
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">590
+</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
+          <t xml:space="preserve">8319
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">675
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">2008
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3028
+          <t xml:space="preserve">12630
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">23318
 </t>
         </is>
       </c>
@@ -6912,140 +6814,135 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">4178
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11014
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810154
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
+          <t xml:space="preserve">621
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1111819
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1970
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">064
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 47
+</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1886
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112138
-</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11019
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1321
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0241
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13654
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">541
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218416
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="n"/>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">18624
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
@@ -626,127 +626,127 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3012
+          <t xml:space="preserve">2891
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1197
+</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">97
 </t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1119
-</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9280
-</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4625
-</t>
-        </is>
-      </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -756,18 +756,8 @@
 </t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">738
-</t>
-        </is>
-      </c>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -782,141 +772,145 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3824
+          <t xml:space="preserve">146495
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181494
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr"/>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4695
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -933,43 +927,43 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">3380
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -981,100 +975,90 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">12561
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">029
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="n"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1089,145 +1073,145 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2758
+          <t xml:space="preserve">3537
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0177
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1245,144 +1229,145 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
+          <t xml:space="preserve">3779
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2673
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1131
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">72
 </t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227194
-</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1400,143 +1385,140 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>439274</t>
+          <t xml:space="preserve">18252
+</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">713
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">550
 </t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">919
-</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">739
-</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
-</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t xml:space="preserve">749
+</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6848
+          <t xml:space="preserve">4220
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
+          <t xml:space="preserve">1033
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">92856
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38015
+          <t xml:space="preserve">8911
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">955
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">8712
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94145
+          <t xml:space="preserve">94298
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -1554,140 +1536,145 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
+          <t xml:space="preserve">36501
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 2
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24181
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1113
-</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1110
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2130
-</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">968
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 24
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1705,140 +1692,145 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5093
+          <t xml:space="preserve">3296
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10479
+          <t xml:space="preserve">1333
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">097
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 316
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">1023
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">2899
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5120
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">11886
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">2184
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -1856,145 +1848,140 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5061
+          <t xml:space="preserve">5011
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2059
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">2198
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">01100
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11917
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8221
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2012,145 +1999,145 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3579
+          <t xml:space="preserve">1556
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1112
 </t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17915
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2168,140 +2155,145 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">0329
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">0145
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2158
+          <t xml:space="preserve">1125
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr"/>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1711
+</t>
+        </is>
+      </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">087
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2319,97 +2311,97 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310
+          <t xml:space="preserve">4545
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2421,43 +2413,43 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">2480
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -2475,144 +2467,145 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22271
+          <t xml:space="preserve">23069
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">6553
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">957
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1349
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">669
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
+          <t xml:space="preserve">4930
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11110
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3109
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8017
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3690
+          <t xml:space="preserve">94210
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -2630,139 +2623,144 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4459
+          <t xml:space="preserve">08141
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98718
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1136
-</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 8
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1169
-</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t xml:space="preserve">626
+</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2780,145 +2778,140 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">9557
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116666
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">9828
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">12168
 </t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21104
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">2102
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">16 7
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -2936,145 +2929,145 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1630
+</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">106
 </t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21112
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 0
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0094
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3092,145 +3085,140 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5422
+          <t xml:space="preserve">14979
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22110
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">405
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1912
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12997
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3248,148 +3236,143 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3824
+          <t xml:space="preserve">3713
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">2163
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0159
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">809
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="n"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3404,67 +3387,66 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94890
+          <t xml:space="preserve">5089
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">11209
 </t>
         </is>
       </c>
@@ -3476,73 +3458,73 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">12246
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">18 54
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1497
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3560,144 +3542,134 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123203
+          <t xml:space="preserve">20894
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">11284
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2611
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4890
+</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">781
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9185
+</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357
-</t>
+          <t>32606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">0498
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3415
+          <t xml:space="preserve">4298
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">1983
 </t>
         </is>
       </c>
@@ -3715,139 +3687,140 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24641
+          <t xml:space="preserve">49129
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1571
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7161
+          <t xml:space="preserve">371
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">0944
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11771
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3865,145 +3838,144 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14889
+          <t xml:space="preserve">2236
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">23 1
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2415
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01132
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1719
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82169
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">9208
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4021,145 +3993,140 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
+          <t xml:space="preserve">2683
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51094
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">9088
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4177,144 +4144,140 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402
+          <t xml:space="preserve">4358
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">01312
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1088
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">880
 </t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116182
-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1185
-</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4332,145 +4295,145 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11565
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">87
 </t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19354
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28170
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4488,145 +4451,139 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233
+          <t xml:space="preserve">3091
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1181
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">661
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1270
-</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11817
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4644,140 +4601,140 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22848
+          <t xml:space="preserve">15699
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1312
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
+          <t xml:space="preserve">6459
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">743
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">690
+</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4918
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3148
+          <t xml:space="preserve">4131
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">995
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
+          <t xml:space="preserve">942280
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -4795,140 +4752,130 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320
+          <t xml:space="preserve">3140
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26 2
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1584
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16441
+</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7193
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">92116
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111 1
+          <t xml:space="preserve">044
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr"/>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4946,140 +4893,144 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52808
+          <t xml:space="preserve">3642
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1105
-</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2201
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="n"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">094
+</t>
+        </is>
+      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1700
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5097,143 +5048,148 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
+          <t xml:space="preserve">4112
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11114
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">2115
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1601
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1194
-</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">0165
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="n"/>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>22</t>
@@ -5248,142 +5204,143 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
+          <t xml:space="preserve">2114
 </t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">15719
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1497
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">023
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">17
 </t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1159
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9910
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1187
-</t>
-        </is>
-      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="2" t="n"/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -5398,61 +5355,61 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5462,81 +5419,76 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">688
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8168
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6835
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5554,49 +5506,49 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355
+          <t xml:space="preserve">6132
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11054
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">0195
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5608,88 +5560,94 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">8708
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5704,72 +5662,73 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t xml:space="preserve">20782
+</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">11184
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6726
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417
+          <t xml:space="preserve">1814
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5781,66 +5740,67 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38019
+</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">880
 </t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2169
-</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">545
-</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1009
-</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8371
-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
+          <t xml:space="preserve">4222
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">394
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -5858,69 +5818,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481
+          <t xml:space="preserve">4156
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>837</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">10351
+</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1665
+</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11702
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1135
 </t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">901
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1130
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5931,67 +5894,67 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 8
+          <t xml:space="preserve">02 4
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11276
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1 6 1
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6009,137 +5972,142 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5799
+          <t xml:space="preserve">6244
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="n"/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">051
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1025
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8157
+          <t xml:space="preserve">0625
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="2" t="n"/>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -6154,25 +6122,25 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">6377
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -6182,19 +6150,19 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
+      <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6203,81 +6171,91 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">489
+</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="n"/>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6295,39 +6273,44 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
+          <t xml:space="preserve">6993
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6339,19 +6322,20 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 6
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -6368,64 +6352,59 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">1722
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4235
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">26417
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0198
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">390
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="n"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6440,49 +6419,49 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113517
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6494,74 +6473,89 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">046
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">435
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="n"/>
-      <c r="X42" s="2" t="n"/>
-      <c r="Y42" s="2" t="n"/>
-      <c r="Z42" s="2" t="n"/>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6576,33 +6570,138 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
+          <t xml:space="preserve">50494
+</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2" t="n"/>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n"/>
-      <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="n"/>
-      <c r="S43" s="2" t="n"/>
-      <c r="T43" s="2" t="n"/>
-      <c r="U43" s="2" t="n"/>
-      <c r="V43" s="2" t="n"/>
-      <c r="W43" s="2" t="n"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 279
+</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11227
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9720
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="X43" s="2" t="n"/>
-      <c r="Y43" s="2" t="n"/>
-      <c r="Z43" s="2" t="n"/>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">398
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2109
+</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>30</t>
@@ -6658,145 +6757,144 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19112
+          <t xml:space="preserve">31195
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10917
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">775
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3880
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
+          <t xml:space="preserve">21725
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8319
+          <t xml:space="preserve">1089
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">675
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12630
+          <t xml:space="preserve">3028
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23318
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -6814,135 +6912,140 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4178
+          <t xml:space="preserve">2239
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">11014
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">810154
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111819
+          <t xml:space="preserve">112138
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">11019
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">0241
 </t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 47
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">541
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">598
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13654
+</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">218416
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="n"/>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18624
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -692,7 +692,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -704,13 +704,13 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -728,7 +728,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -740,7 +740,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">0178
 </t>
         </is>
       </c>
@@ -756,7 +756,12 @@
 </t>
         </is>
       </c>
-      <c r="Y4" s="2" t="n"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
@@ -772,13 +777,13 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146495
+          <t xml:space="preserve">4645
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -844,13 +849,13 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -862,13 +867,13 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -892,7 +897,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -902,15 +907,11 @@
 </t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
+      <c r="Y5" s="2" t="n"/>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -933,37 +934,37 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -981,19 +982,19 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1942
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12561
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -1018,7 +1019,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1048,17 +1049,22 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">930
 </t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1073,7 +1079,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3537
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
@@ -1145,7 +1151,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1163,7 +1169,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1175,7 +1181,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -1187,7 +1193,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -1199,7 +1205,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -1211,7 +1217,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -1253,7 +1259,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
@@ -1295,13 +1301,13 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1331,7 +1337,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1385,7 +1391,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18252
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
@@ -1397,8 +1403,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">713
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1425,7 +1430,12 @@
 </t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">289
@@ -1440,25 +1450,25 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1476,13 +1486,13 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92856
+          <t xml:space="preserve">1986
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8911
+          <t xml:space="preserve">8918
 </t>
         </is>
       </c>
@@ -1494,13 +1504,13 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8712
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
@@ -1512,13 +1522,13 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94298
+          <t xml:space="preserve">94290
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -1536,7 +1546,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36501
+          <t xml:space="preserve">3650
 </t>
         </is>
       </c>
@@ -1560,7 +1570,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1584,25 +1594,25 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -1614,13 +1624,13 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 2
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -1638,19 +1648,19 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">11914
 </t>
         </is>
       </c>
@@ -1692,25 +1702,25 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
+          <t xml:space="preserve">3246
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1333
+          <t xml:space="preserve">753
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1553
 </t>
         </is>
       </c>
@@ -1734,103 +1744,103 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">097
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1179
+</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11228
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2136
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1023
+</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12204
+</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 316
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1023
-</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2899
-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11886
+          <t xml:space="preserve">11586
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -1848,13 +1858,13 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5011
+          <t xml:space="preserve">5111
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -1866,7 +1876,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1878,17 +1888,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01100
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -1897,55 +1912,55 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -1975,13 +1990,13 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2810
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1999,7 +2014,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
@@ -2011,7 +2026,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
@@ -2023,7 +2038,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2047,25 +2062,25 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2077,7 +2092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">982
 </t>
         </is>
       </c>
@@ -2089,19 +2104,18 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">18668
 </t>
         </is>
       </c>
@@ -2131,7 +2145,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
@@ -2155,7 +2169,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0329
+          <t xml:space="preserve">3319
 </t>
         </is>
       </c>
@@ -2173,13 +2187,13 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2209,19 +2223,19 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2233,7 +2247,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2257,13 +2271,13 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">711
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -2275,19 +2289,19 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2311,7 +2325,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4545
+          <t xml:space="preserve">4845
 </t>
         </is>
       </c>
@@ -2335,7 +2349,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -2347,19 +2361,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2377,13 +2391,13 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -2413,7 +2427,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
@@ -2437,7 +2451,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2449,7 +2463,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -2479,7 +2493,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6553
+          <t xml:space="preserve">652
 </t>
         </is>
       </c>
@@ -2491,7 +2505,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
@@ -2509,13 +2523,13 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1349
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2527,31 +2541,25 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4930
-</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4320
+</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
@@ -2575,31 +2583,31 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">2558
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94210
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
@@ -2623,31 +2631,31 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08141
+          <t xml:space="preserve">4614
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">21124
 </t>
         </is>
       </c>
@@ -2665,18 +2673,19 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2694,7 +2703,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -2712,7 +2721,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2730,13 +2739,13 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">2014
 </t>
         </is>
       </c>
@@ -2760,7 +2769,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -2778,13 +2787,13 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9557
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
@@ -2808,14 +2817,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2833,19 +2847,19 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9828
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -2857,7 +2871,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12168
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -2875,25 +2889,25 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 7
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -2941,7 +2955,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630
+          <t xml:space="preserve">2130
 </t>
         </is>
       </c>
@@ -2953,13 +2967,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
@@ -2971,13 +2985,13 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
@@ -2989,20 +3003,19 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3013,7 +3026,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -3025,7 +3038,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1794
 </t>
         </is>
       </c>
@@ -3037,13 +3050,13 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -3055,7 +3068,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3085,7 +3098,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14979
+          <t xml:space="preserve">14179
 </t>
         </is>
       </c>
@@ -3097,7 +3110,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">11254
 </t>
         </is>
       </c>
@@ -3149,11 +3162,15 @@
 </t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3164,7 +3181,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -3182,43 +3199,43 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">8 0
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3236,7 +3253,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">3793
 </t>
         </is>
       </c>
@@ -3248,7 +3265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">0140
 </t>
         </is>
       </c>
@@ -3260,7 +3277,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3272,7 +3289,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3284,7 +3301,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
@@ -3296,13 +3313,13 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3326,7 +3343,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3344,7 +3361,7 @@
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -3356,23 +3373,28 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="n"/>
+          <t xml:space="preserve">9181
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3399,19 +3421,20 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">11132
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3446,7 +3469,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11209
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3458,43 +3481,43 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">2970
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 54
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -3512,7 +3535,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -3548,7 +3571,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11284
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
@@ -3566,7 +3589,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
@@ -3578,8 +3601,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>013</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -3590,13 +3612,13 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">807
 </t>
         </is>
       </c>
@@ -3608,8 +3630,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -3618,7 +3639,12 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1156
@@ -3627,19 +3653,20 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9185
+          <t xml:space="preserve">1915
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t xml:space="preserve">2328
+</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0498
+          <t xml:space="preserve">1498
 </t>
         </is>
       </c>
@@ -3657,7 +3684,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -3669,7 +3696,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -3687,13 +3714,13 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49129
+          <t xml:space="preserve">4179
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">0236
 </t>
         </is>
       </c>
@@ -3705,19 +3732,19 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -3729,14 +3756,14 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -3748,7 +3775,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3760,7 +3787,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0944
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3784,7 +3811,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -3796,7 +3823,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -3808,7 +3835,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -3820,7 +3847,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3838,19 +3865,19 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">2336
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 1
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -3862,7 +3889,8 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">76
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3873,7 +3901,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -3885,25 +3913,25 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3915,13 +3943,13 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3945,37 +3973,36 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3993,7 +4020,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2683
+          <t xml:space="preserve">2283
 </t>
         </is>
       </c>
@@ -4017,13 +4044,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4033,7 +4060,12 @@
 </t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">177
@@ -4054,19 +4086,19 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -4078,19 +4110,19 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4108,28 +4140,18 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="n"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -4144,7 +4166,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4358
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
@@ -4168,7 +4190,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01312
+          <t xml:space="preserve">10122
 </t>
         </is>
       </c>
@@ -4180,7 +4202,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4198,19 +4220,19 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">1735
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1088
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -4228,7 +4250,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -4244,16 +4266,20 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -4313,7 +4339,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4331,7 +4357,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4355,7 +4381,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4367,7 +4393,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -4391,19 +4417,19 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -4451,7 +4477,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">3097
 </t>
         </is>
       </c>
@@ -4463,20 +4489,25 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -4500,7 +4531,8 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">1137
+</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -4511,19 +4543,18 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -4541,13 +4572,13 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -4559,19 +4590,19 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -4601,7 +4632,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15699
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -4625,13 +4656,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6459
+          <t xml:space="preserve">449
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">624
 </t>
         </is>
       </c>
@@ -4643,19 +4674,19 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">76 9
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">749
 </t>
         </is>
       </c>
@@ -4667,14 +4698,13 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr"/>
@@ -4692,7 +4722,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
@@ -4716,25 +4746,25 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8249
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942280
+          <t xml:space="preserve">94280
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -4758,13 +4788,13 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -4788,7 +4818,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4798,12 +4828,7 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1150
@@ -4812,18 +4837,28 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n"/>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16441
-</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">604
+</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001
+</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -4832,7 +4867,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
@@ -4844,19 +4879,19 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92116
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">011
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">17 0
 </t>
         </is>
       </c>
@@ -4866,7 +4901,12 @@
 </t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">950
@@ -4875,7 +4915,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4899,66 +4939,67 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2207
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t xml:space="preserve">391
+</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">5716
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4976,34 +5017,24 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
+      <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1166
@@ -5018,19 +5049,19 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -5066,7 +5097,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
@@ -5078,19 +5109,19 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5102,19 +5133,19 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601
+          <t xml:space="preserve">191619
 </t>
         </is>
       </c>
@@ -5144,49 +5175,49 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">28809
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5210,13 +5241,13 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15719
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -5228,13 +5259,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -5246,13 +5277,13 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">023
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5262,7 +5293,12 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">170
@@ -5271,7 +5307,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5283,7 +5319,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5295,13 +5331,13 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
@@ -5319,7 +5355,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
@@ -5331,7 +5367,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">1900
 </t>
         </is>
       </c>
@@ -5355,25 +5391,25 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
@@ -5385,7 +5421,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5415,11 +5451,16 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1123
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -5428,13 +5469,13 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -5446,13 +5487,13 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1 1 9
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
@@ -5464,31 +5505,31 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
@@ -5518,25 +5559,25 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -5560,25 +5601,25 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -5590,7 +5631,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -5608,13 +5649,13 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5638,13 +5679,13 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5668,67 +5709,67 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">3523
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">5079
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -5740,7 +5781,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5752,7 +5793,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">599
 </t>
         </is>
       </c>
@@ -5764,7 +5805,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38019
+          <t xml:space="preserve">3809
 </t>
         </is>
       </c>
@@ -5776,7 +5817,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">700
 </t>
         </is>
       </c>
@@ -5794,16 +5835,11 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4222
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4298
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5824,7 +5860,8 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5841,31 +5878,31 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10351
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11702
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -5877,13 +5914,14 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5894,7 +5932,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02 4
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
@@ -5906,55 +5944,55 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1176
 </t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 6 1
-</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -5972,7 +6010,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6244
+          <t xml:space="preserve">6243
 </t>
         </is>
       </c>
@@ -5984,7 +6022,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6008,20 +6046,25 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="n"/>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
@@ -6033,13 +6076,14 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t xml:space="preserve">910
+</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -6050,22 +6094,17 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="n"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -6080,19 +6119,19 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2715
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0625
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6104,7 +6143,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -6134,7 +6173,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -6146,11 +6185,16 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="n"/>
+          <t xml:space="preserve">1653
+</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">38
@@ -6195,7 +6239,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6213,13 +6257,13 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">19488
 </t>
         </is>
       </c>
@@ -6231,7 +6275,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6247,15 +6291,10 @@
 </t>
         </is>
       </c>
-      <c r="Y40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">628
-</t>
-        </is>
-      </c>
+      <c r="Y40" s="2" t="n"/>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6273,7 +6312,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6993
+          <t xml:space="preserve">6443
 </t>
         </is>
       </c>
@@ -6285,13 +6324,13 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -6302,15 +6341,10 @@
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -6322,25 +6356,25 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1015
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -6358,49 +6392,49 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1722
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9470
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26417
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
@@ -6431,31 +6465,31 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">4709
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -6467,26 +6501,31 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n"/>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6498,7 +6537,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -6508,42 +6547,37 @@
 </t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">610
@@ -6552,7 +6586,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6570,7 +6604,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50494
+          <t xml:space="preserve">6044
 </t>
         </is>
       </c>
@@ -6582,14 +6616,19 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="n"/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 279
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6619,86 +6658,90 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1207
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91209
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2392
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1130
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11227
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9720
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="n"/>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
@@ -6763,7 +6806,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
@@ -6781,7 +6824,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
+          <t xml:space="preserve">772
 </t>
         </is>
       </c>
@@ -6799,43 +6842,42 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">1559
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">1619
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">94980
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6853,19 +6895,20 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21725
+          <t xml:space="preserve">2825
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -6876,19 +6919,19 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">106888
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3028
+          <t xml:space="preserve">23028
 </t>
         </is>
       </c>
@@ -6924,19 +6967,19 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11014
+          <t xml:space="preserve">11017
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810154
+          <t xml:space="preserve">1513
 </t>
         </is>
       </c>
@@ -6954,43 +6997,43 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">111119
 </t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112138
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11019
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0241
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -7002,35 +7045,40 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13654
+          <t xml:space="preserve">0654
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218416
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">160
@@ -7039,13 +7087,13 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
@@ -626,140 +626,117 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
-</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n"/>
@@ -777,141 +754,118 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
-</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y5" s="2" t="n"/>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -928,141 +882,118 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
-</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1942
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1079,146 +1010,122 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1235,146 +1142,122 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
-</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1391,14 +1274,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
-</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1408,128 +1289,107 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>841</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
-</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8918
-</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>955</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,146 +1406,122 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>111001</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11914
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,146 +1538,122 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3246
-</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">753
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11228
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12204
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11586
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1858,146 +1670,122 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2810
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2014,92 +1802,77 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
-</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -2109,50 +1882,42 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2169,146 +1934,122 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3319
-</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
-</t>
+          <t>711</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2325,146 +2066,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
-</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2481,68 +2198,57 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23069
-</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">652
-</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">669
-</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2552,69 +2258,58 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
-</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>998</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2631,146 +2326,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4614
-</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2787,146 +2458,122 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
-</t>
+          <t>680</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2943,74 +2590,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -3020,68 +2655,57 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3098,74 +2722,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11254
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -3175,68 +2787,57 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 0
-</t>
+          <t>12 0</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3253,146 +2854,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
-</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
-</t>
+          <t>809</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9181
-</t>
+          <t>981</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3409,146 +2986,122 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11132
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3565,38 +3118,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20894
-</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
-</t>
+          <t>539</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3606,26 +3153,22 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3635,69 +3178,58 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
-</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3714,141 +3246,122 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0236
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3865,128 +3378,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
-</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
@@ -3996,14 +3488,12 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4020,135 +3510,113 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283
-</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z26" s="2" t="n"/>
@@ -4166,110 +3634,92 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10122
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1735
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -4279,32 +3729,27 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4321,146 +3766,122 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
-</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4477,68 +3898,57 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3097
-</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -4548,74 +3958,62 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4632,74 +4030,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">449
-</t>
+          <t>449</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76 9
-</t>
+          <t>76 9</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4710,62 +4096,52 @@
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>994</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94280
-</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4782,141 +4158,118 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140
-</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 0
-</t>
+          <t>17 0</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4933,136 +4286,114 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3642
-</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
+          <t>393</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5079,146 +4410,122 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191619
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28809
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5235,146 +4542,122 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114
-</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 1
-</t>
+          <t>115 0</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5391,146 +4674,122 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1 9
-</t>
+          <t>8 9</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">608
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5547,146 +4806,122 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5703,140 +4938,117 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20782
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3523
-</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079
-</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>771</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
-</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
-</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
-</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
-</t>
+          <t>700</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr"/>
@@ -5854,146 +5066,122 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6010,141 +5198,118 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2715
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6161,141 +5326,118 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
-</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="Y40" s="2" t="n"/>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6312,130 +5454,109 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6443
-</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z41" s="2" t="n"/>
@@ -6453,141 +5574,118 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
-</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4709
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6604,98 +5702,82 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
-</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -6705,44 +5787,37 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91209
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6759,8 +5834,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -6800,44 +5874,37 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
-</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
-</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
-</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -6847,98 +5914,82 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1559
-</t>
+          <t>559</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94980
-</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825
-</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
-</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106888
-</t>
+          <t>608</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028
-</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6955,146 +6006,122 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
-</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11017
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1513
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111119
-</t>
+          <t>1111111110</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>505</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0654
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
@@ -958,12 +958,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>675</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>0101</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>286</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>143</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>993</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>154</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>141</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>262</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>656</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>71 2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1168 2</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>904</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>149 1</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>916</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17 0</t>
+          <t>17 04</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1815 0</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>323</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>219</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>115 0</t>
+          <t>115 00</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>291</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>960</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8 9</t>
+          <t>2 7 9</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>541</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3809 1</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>900</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5501,12 +5501,12 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>322</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>189</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>659</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>260</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1111111110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">

--- a/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Top_Excel_with_OCR_Results.xlsx
@@ -958,7 +958,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>895</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0101</t>
+          <t>210</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>301</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>998</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>561</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12 0</t>
+          <t>02 0</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>508</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>173</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71 2</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>139</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1168 2</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4209,17 +4209,17 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>856</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17 04</t>
+          <t>17 00</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1815 0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -4331,22 +4331,22 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>181</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>211</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>115 00</t>
+          <t>15 0</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>900</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2 7 9</t>
+          <t>2 1 2 8</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>581</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>078</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3809 1</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>488</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       <c r="Y40" s="2" t="n"/>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -5924,17 +5924,17 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>554</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>654</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>505</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
